--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260703.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>81,526</t>
+          <t>53,001</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>53,001</t>
+          <t>81,526</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
